--- a/public/template/template_bulk_agi_mtm.xlsx
+++ b/public/template/template_bulk_agi_mtm.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\mtm\public\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\apuppt\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42044E94-39D3-46E0-A9EF-0D099C3C1EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375CD1D2-1BAB-4F5C-ADC1-894B3EEFF41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -30,21 +33,12 @@
     <t>Nominal</t>
   </si>
   <si>
-    <t>User Code 1</t>
-  </si>
-  <si>
-    <t>User Code 2</t>
-  </si>
-  <si>
     <t>Keterangan 1</t>
   </si>
   <si>
     <t>Keterangan 2</t>
   </si>
   <si>
-    <t>nomor transaksi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rekening Eksternal </t>
   </si>
   <si>
@@ -64,19 +58,35 @@
   </si>
   <si>
     <t>Indikator</t>
+  </si>
+  <si>
+    <t>Refference</t>
+  </si>
+  <si>
+    <t>Cost Center 1</t>
+  </si>
+  <si>
+    <t>Cost Center 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -114,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -126,6 +136,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,60 +417,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.77734375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J2" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="10">
@@ -478,8 +492,8 @@
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Rekening Eksternal" error="Inputan tidak boleh kurang atau lebih dari 13 karakter." promptTitle="Input Validation" prompt="Inputan tidak boleh kurang atau lebih dari 13 karakter." sqref="B2:B1048576" xr:uid="{D63491A6-D9A0-4933-9436-9AC885D3830C}">
       <formula1>13</formula1>
     </dataValidation>
-    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 1" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="J2:J1048576" xr:uid="{722273AA-008D-4AFB-9109-1516AC082185}">
-      <formula1>AND(ISERROR(FIND("?",J2)), ISERROR(FIND(":",J2)), ISERROR(FIND("*",J2)), LEN(J2)&lt;=35)</formula1>
+    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 1" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="J3:J1048576" xr:uid="{722273AA-008D-4AFB-9109-1516AC082185}">
+      <formula1>AND(ISERROR(FIND("?",J3)), ISERROR(FIND(":",J3)), ISERROR(FIND("*",J3)), LEN(J3)&lt;=35)</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Keterangan 2" error="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." promptTitle="Input Validation" prompt="Tidak diperbolehkan menggunakan spesial karakter * ? :  dan panjang teks tidak boleh melebihi 35 karakter." sqref="K2:K1048576" xr:uid="{2602352D-8A01-4165-9A7F-0D398AC81B79}">
       <formula1>AND(ISERROR(FIND("?",K2)), ISERROR(FIND(":",K2)), ISERROR(FIND("*",K2)), LEN(K2)&lt;=35)</formula1>

--- a/public/template/template_bulk_agi_mtm.xlsx
+++ b/public/template/template_bulk_agi_mtm.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\apuppt\public\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\cekstatus\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375CD1D2-1BAB-4F5C-ADC1-894B3EEFF41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972660FB-9D1A-400E-9813-0A8414AAEE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -420,19 +420,19 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.77734375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -453,10 +453,10 @@
       <c r="G1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="J1" s="1" t="s">
